--- a/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F87CF09-DA40-4BD9-AA09-5D52EF506927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34C0ABB-B836-49EE-A899-93E508F87C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="77">
   <si>
     <t>Booking</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>Not Available</t>
+  </si>
+  <si>
+    <t>Resigned</t>
   </si>
 </sst>
 </file>
@@ -1498,7 +1501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -1519,9 +1522,10 @@
     <col min="19" max="19" width="8.7265625" customWidth="1"/>
     <col min="20" max="22" width="7.1796875" customWidth="1"/>
     <col min="23" max="23" width="20.453125" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G1" s="101" t="s">
         <v>0</v>
       </c>
@@ -1543,9 +1547,9 @@
       <c r="U1" s="105"/>
       <c r="V1" s="106"/>
     </row>
-    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1572,7 +1576,7 @@
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
-    <row r="3" spans="1:23" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:28" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="25" t="s">
         <v>4</v>
       </c>
@@ -1643,7 +1647,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="29" t="s">
         <v>20</v>
       </c>
@@ -1666,61 +1670,61 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.28000000000000003</v>
+        <v>0.32</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>17.850000000000001</v>
+        <v>20</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.44625000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.2750000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.59375</v>
+        <v>1.5625</v>
       </c>
       <c r="O4" s="30">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P4" s="96">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="R4" s="30">
         <v>17.850000000000001</v>
       </c>
       <c r="S4" s="96">
-        <v>17.850000000000001</v>
+        <v>18</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>1</v>
+        <v>1.0084033613445378</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>0.89250000000000007</v>
+        <v>1.2857142857142858</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.1524609843937574</v>
       </c>
       <c r="W4" s="34"/>
     </row>
-    <row r="5" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
         <v>20</v>
       </c>
@@ -1743,61 +1747,61 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>10.25</v>
+        <v>9</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.34166666666666667</v>
+        <v>0.3</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>2.0499999999999998</v>
+        <v>1.2857142857142858</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>3.4166666666666665</v>
+        <v>2.1428571428571428</v>
       </c>
       <c r="O5" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" s="97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R5" s="30">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="S5" s="97">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.8936170212765957</v>
+        <v>0.9</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>0.8936170212765957</v>
+        <v>0.9</v>
       </c>
       <c r="W5" s="34"/>
     </row>
-    <row r="6" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
         <v>20</v>
       </c>
@@ -1864,7 +1868,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
         <v>20</v>
       </c>
@@ -1887,61 +1891,61 @@
         <v>50</v>
       </c>
       <c r="H7" s="12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
       <c r="K7" s="12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N7" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>1.6666666666666665</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O7" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P7" s="97">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="13">
         <f t="shared" si="3"/>
-        <v>0.33333333333333331</v>
+        <v>0.8</v>
       </c>
       <c r="R7" s="30">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="S7" s="97">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>0.46153846153846156</v>
+        <v>1</v>
       </c>
       <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="V7" s="14">
         <f t="shared" si="5"/>
-        <v>1.3846153846153848</v>
+        <v>1.25</v>
       </c>
       <c r="W7" s="34"/>
     </row>
-    <row r="8" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
         <v>20</v>
       </c>
@@ -1964,61 +1968,61 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.55000000000000004</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>1.375</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>3.4375</v>
+        <v>5.7499999999999991</v>
       </c>
       <c r="O8" s="30">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P8" s="97">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="R8" s="30">
-        <v>19.649999999999999</v>
+        <v>8</v>
       </c>
       <c r="S8" s="97">
-        <v>15.65</v>
+        <v>5</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.79643765903307895</v>
+        <v>0.625</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>1.4227272727272728</v>
+        <v>1</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>0.79643765903307895</v>
+        <v>1</v>
       </c>
       <c r="W8" s="34"/>
     </row>
-    <row r="9" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
         <v>20</v>
       </c>
@@ -2085,7 +2089,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="35" t="s">
         <v>20</v>
       </c>
@@ -2107,58 +2111,65 @@
       <c r="G10" s="30">
         <v>25</v>
       </c>
-      <c r="H10" s="12"/>
+      <c r="H10" s="12">
+        <v>14</v>
+      </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
-      <c r="K10" s="12"/>
+      <c r="K10" s="12">
+        <v>619</v>
+      </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M10" s="11" t="e">
+      <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>44.214285714285715</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P10" s="97">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>0.45454545454545453</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="R10" s="30">
-        <v>177</v>
+        <v>71</v>
       </c>
       <c r="S10" s="97">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0.40112994350282488</v>
+        <v>0.81690140845070425</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>14.2</v>
+        <v>8.2857142857142865</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>0.88248587570621473</v>
+        <v>1.0503018108651911</v>
       </c>
       <c r="W10" s="34"/>
-    </row>
-    <row r="11" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="AB10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="35" t="s">
         <v>20</v>
       </c>
@@ -2222,8 +2233,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="W11" s="34"/>
-    </row>
-    <row r="12" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="AB11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A12" s="35" t="s">
         <v>20</v>
       </c>
@@ -2287,8 +2301,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="W12" s="34"/>
-    </row>
-    <row r="13" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="AB12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A13" s="35" t="s">
         <v>20</v>
       </c>
@@ -2324,8 +2341,11 @@
       <c r="U13" s="11"/>
       <c r="V13" s="14"/>
       <c r="W13" s="34"/>
-    </row>
-    <row r="14" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="AB13">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A14" s="35" t="s">
         <v>20</v>
       </c>
@@ -2361,8 +2381,11 @@
       <c r="U14" s="11"/>
       <c r="V14" s="14"/>
       <c r="W14" s="34"/>
-    </row>
-    <row r="15" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="AB14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A15" s="35" t="s">
         <v>20</v>
       </c>
@@ -2398,8 +2421,11 @@
       <c r="U15" s="11"/>
       <c r="V15" s="14"/>
       <c r="W15" s="34"/>
-    </row>
-    <row r="16" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="AB15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A16" s="35" t="s">
         <v>20</v>
       </c>
@@ -2433,8 +2459,11 @@
       <c r="U16" s="11"/>
       <c r="V16" s="14"/>
       <c r="W16" s="34"/>
-    </row>
-    <row r="17" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="AB16">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A17" s="35" t="s">
         <v>20</v>
       </c>
@@ -2470,8 +2499,11 @@
       <c r="U17" s="11"/>
       <c r="V17" s="14"/>
       <c r="W17" s="34"/>
-    </row>
-    <row r="18" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="AB17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A18" s="35" t="s">
         <v>20</v>
       </c>
@@ -2507,8 +2539,11 @@
       <c r="U18" s="36"/>
       <c r="V18" s="39"/>
       <c r="W18" s="34"/>
-    </row>
-    <row r="19" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AB18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="35" t="s">
         <v>20</v>
       </c>
@@ -2529,11 +2564,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>8.533333333333333E-2</v>
+        <v>0.12533333333333332</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2541,15 +2576,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>44.1</v>
+        <v>671</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.11454545454545455</v>
+        <v>1.7428571428571429</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>1.378125</v>
+        <v>14.276595744680851</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2557,39 +2592,42 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.80769230769230771</v>
+        <v>0.81395348837209303</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>230.4</v>
+        <v>110.85</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>115.9</v>
+        <v>94</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.50303819444444442</v>
+        <v>0.84799278304014436</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>2.7595238095238095</v>
+        <v>2.6857142857142855</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="W19" s="44"/>
-    </row>
-    <row r="20" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="AB19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A20" s="35" t="s">
         <v>20</v>
       </c>
@@ -2663,8 +2701,11 @@
         <v>1</v>
       </c>
       <c r="W20" s="34"/>
-    </row>
-    <row r="21" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="AB20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A21" s="35" t="s">
         <v>20</v>
       </c>
@@ -2738,8 +2779,11 @@
         <v>1</v>
       </c>
       <c r="W21" s="34"/>
-    </row>
-    <row r="22" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="AB21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A22" s="35" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2857,11 @@
         <v>1</v>
       </c>
       <c r="W22" s="34"/>
-    </row>
-    <row r="23" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="AB22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A23" s="35" t="s">
         <v>20</v>
       </c>
@@ -2888,8 +2935,11 @@
         <v>1</v>
       </c>
       <c r="W23" s="34"/>
-    </row>
-    <row r="24" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="AB23">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" s="35" t="s">
         <v>20</v>
       </c>
@@ -2964,7 +3014,7 @@
       </c>
       <c r="W24" s="34"/>
     </row>
-    <row r="25" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="35" t="s">
         <v>20</v>
       </c>
@@ -3045,7 +3095,7 @@
       </c>
       <c r="W25" s="44"/>
     </row>
-    <row r="26" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A26" s="35" t="s">
         <v>20</v>
       </c>
@@ -3120,7 +3170,7 @@
       </c>
       <c r="W26" s="34"/>
     </row>
-    <row r="27" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A27" s="35" t="s">
         <v>20</v>
       </c>
@@ -3195,7 +3245,7 @@
       </c>
       <c r="W27" s="34"/>
     </row>
-    <row r="28" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:28" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A28" s="35" t="s">
         <v>20</v>
       </c>
@@ -3270,7 +3320,7 @@
       </c>
       <c r="W28" s="34"/>
     </row>
-    <row r="29" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A29" s="35" t="s">
         <v>20</v>
       </c>
@@ -3345,7 +3395,7 @@
       </c>
       <c r="W29" s="34"/>
     </row>
-    <row r="30" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="35" t="s">
         <v>20</v>
       </c>
@@ -3426,7 +3476,7 @@
       </c>
       <c r="W30" s="44"/>
     </row>
-    <row r="31" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="45" t="s">
         <v>20</v>
       </c>
@@ -3443,11 +3493,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.6198347107438019E-2</v>
+        <v>6.1157024793388429E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3455,15 +3505,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>211.1</v>
+        <v>838</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>8.1663442940038689E-2</v>
+        <v>0.32417794970986458</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.2417647058823529</v>
+        <v>4.5297297297297296</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3471,31 +3521,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.77114427860696522</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>469.4</v>
+        <v>349.85</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>245.9</v>
+        <v>224</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.52386024712398815</v>
+        <v>0.64027440331570673</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.5864516129032258</v>
+        <v>1.5135135135135136</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3560,18 +3610,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.62962962962962965</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="94">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3666,34 +3716,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11+8+11+8+16</f>
-        <v>107</v>
+        <f>5+9+9+11+10+9+11+8+11+8+16+14</f>
+        <v>121</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.17833333333333334</v>
+        <v>0.20166666666666666</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>220</v>
+        <v>238.45</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.38260869565217392</v>
+        <v>0.41469565217391302</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>355</v>
+        <v>336.55</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>35.5</v>
+        <v>37.394444444444446</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>2.05607476635514</v>
+        <v>1.9706611570247934</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3723,38 +3773,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3+2+5+7+14+20</f>
-        <v>94</v>
+        <f>4+8+7+17+7+3+2+5+7+14+20+10</f>
+        <v>104</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.15666666666666668</v>
+        <v>0.17333333333333334</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <v>111</v>
+        <v>120.25</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.20181818181818181</v>
+        <v>0.21863636363636363</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>439</v>
+        <v>429.75</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>43.9</v>
+        <v>47.75</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.1808510638297873</v>
+        <v>1.15625</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.288201160541586</v>
+        <v>1.2613636363636362</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3804,7 +3854,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>50.368000000000002</v>
+        <v>55.964444444444446</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3814,7 +3864,9 @@
         <f t="shared" si="4"/>
         <v>1.8046753246753247</v>
       </c>
-      <c r="Q6" s="34"/>
+      <c r="Q6" s="34" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="7" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -3839,38 +3891,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+13+0+4+3+4+9</f>
-        <v>38</v>
+        <f>5+13+0+4+3+4+9+5</f>
+        <v>43</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>6.3333333333333339E-2</v>
+        <v>7.166666666666667E-2</v>
       </c>
       <c r="J7" s="11">
         <v>550</v>
       </c>
       <c r="K7" s="12">
-        <v>55</v>
+        <v>59.3</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.10781818181818181</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>495</v>
+        <v>490.7</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>49.5</v>
+        <v>54.522222222222219</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.4473684210526316</v>
+        <v>1.3790697674418604</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.5789473684210527</v>
+        <v>1.5044397463002113</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3897,38 +3949,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11+11+8+7+9+24</f>
-        <v>120</v>
+        <f>10+10+0+14+6+10+11+11+8+7+9+24+14</f>
+        <v>134</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.22333333333333333</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>236</v>
+        <v>240.6</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.41043478260869565</v>
+        <v>0.41843478260869565</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>339</v>
+        <v>334.4</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>33.9</v>
+        <v>37.155555555555551</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.9666666666666666</v>
+        <v>1.7955223880597015</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>2.052173913043478</v>
+        <v>1.873588578844906</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -3973,7 +4025,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>55</v>
+        <v>61.111111111111114</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4031,7 +4083,7 @@
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>388.5</v>
+        <v>431.66666666666669</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
@@ -4090,7 +4142,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>63.2</v>
+        <v>70.222222222222229</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4147,7 +4199,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>53.1</v>
+        <v>59</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4347,7 +4399,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>133.33333333333334</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4454,11 +4506,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>471</v>
+        <v>514</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>9.4200000000000006E-2</v>
+        <v>0.1028</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4466,23 +4518,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>1740.32</v>
+        <v>1776.92</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.16310402999062792</v>
+        <v>0.16653420805998126</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>8929.68</v>
+        <v>8893.08</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>892.96800000000007</v>
+        <v>988.12</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.6949469214437367</v>
+        <v>3.4570428015564203</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4535,7 +4587,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>46.5</v>
+        <v>51.666666666666664</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4591,7 +4643,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>46.7</v>
+        <v>51.888888888888886</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4647,7 +4699,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>46.4</v>
+        <v>51.555555555555557</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4703,7 +4755,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>52.555555555555557</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4759,7 +4811,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>48.4</v>
+        <v>53.777777777777779</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4815,7 +4867,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>235.3</v>
+        <v>261.44444444444446</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4872,7 +4924,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>61.6</v>
+        <v>68.444444444444443</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4928,7 +4980,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>56.6</v>
+        <v>62.888888888888886</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4984,7 +5036,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>57.4</v>
+        <v>63.777777777777779</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5040,7 +5092,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>61.2</v>
+        <v>68</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5096,7 +5148,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>236.8</v>
+        <v>263.11111111111109</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5125,11 +5177,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>672</v>
+        <v>715</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.12330275229357798</v>
+        <v>0.13119266055045872</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5137,23 +5189,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>2019.32</v>
+        <v>2055.92</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.12886534779834077</v>
+        <v>0.13120102105934908</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>13650.68</v>
+        <v>13614.08</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>1365.068</v>
+        <v>1512.6755555555555</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.0049404761904759</v>
+        <v>2.8754125874125873</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34C0ABB-B836-49EE-A899-93E508F87C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84277FEB-788F-4790-8AF0-CE2E17CCD28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="79">
   <si>
     <t>Booking</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>Resigned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leave </t>
+  </si>
+  <si>
+    <t>Pending</t>
   </si>
 </sst>
 </file>
@@ -306,6 +312,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1549,7 +1556,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1670,57 +1677,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.25</v>
+        <v>1.0909090909090908</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.5625</v>
+        <v>1.3636363636363635</v>
       </c>
       <c r="O4" s="30">
         <v>16</v>
       </c>
       <c r="P4" s="96">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="R4" s="30">
-        <v>17.850000000000001</v>
+        <v>19.95</v>
       </c>
       <c r="S4" s="96">
-        <v>18</v>
+        <v>19.95</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>1.0084033613445378</v>
+        <v>1</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.2857142857142858</v>
+        <v>1.246875</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>1.1524609843937574</v>
+        <v>1</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1747,59 +1754,61 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1.2857142857142858</v>
+        <v>3.3333333333333335</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>2.1428571428571428</v>
+        <v>5.5555555555555554</v>
       </c>
       <c r="O5" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P5" s="97">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="30">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="S5" s="97">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.9</v>
-      </c>
-      <c r="U5" s="11">
+        <v>0</v>
+      </c>
+      <c r="U5" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>1.8</v>
-      </c>
-      <c r="V5" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V5" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>0.9</v>
-      </c>
-      <c r="W5" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W5" s="34" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="6" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
@@ -1891,134 +1900,128 @@
         <v>50</v>
       </c>
       <c r="H7" s="12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
       <c r="K7" s="12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="e">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="14" t="e">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O7" s="30">
-        <v>5</v>
-      </c>
-      <c r="P7" s="97">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="13">
+        <v>1.9047619047619047</v>
+      </c>
+      <c r="O7" s="30"/>
+      <c r="P7" s="97"/>
+      <c r="Q7" s="13" t="e">
         <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="R7" s="30">
-        <v>4</v>
-      </c>
-      <c r="S7" s="97">
-        <v>4</v>
-      </c>
-      <c r="T7" s="13">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R7" s="30"/>
+      <c r="S7" s="97"/>
+      <c r="T7" s="13" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U7" s="11" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V7" s="14" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W7" s="34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="30">
+        <v>50</v>
+      </c>
+      <c r="H8" s="12">
+        <v>8</v>
+      </c>
+      <c r="I8" s="13">
+        <f t="shared" si="0"/>
+        <v>0.16</v>
+      </c>
+      <c r="J8" s="30">
+        <v>20</v>
+      </c>
+      <c r="K8" s="12">
+        <v>8</v>
+      </c>
+      <c r="L8" s="13">
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+      <c r="M8" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N8" s="14">
+        <f t="shared" si="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="O8" s="30">
+        <v>10</v>
+      </c>
+      <c r="P8" s="97">
+        <v>9</v>
+      </c>
+      <c r="Q8" s="13">
+        <f t="shared" si="3"/>
+        <v>0.9</v>
+      </c>
+      <c r="R8" s="30">
+        <v>20</v>
+      </c>
+      <c r="S8" s="97">
+        <v>20</v>
+      </c>
+      <c r="T8" s="13">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="U7" s="11">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="V7" s="14">
-        <f t="shared" si="5"/>
-        <v>1.25</v>
-      </c>
-      <c r="W7" s="34"/>
-    </row>
-    <row r="8" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="30">
-        <v>50</v>
-      </c>
-      <c r="H8" s="12">
-        <v>10</v>
-      </c>
-      <c r="I8" s="13">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-      <c r="J8" s="30">
-        <v>20</v>
-      </c>
-      <c r="K8" s="12">
-        <v>23</v>
-      </c>
-      <c r="L8" s="13">
-        <f t="shared" si="1"/>
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="M8" s="11">
-        <f t="shared" si="2"/>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="N8" s="14">
-        <f t="shared" si="2"/>
-        <v>5.7499999999999991</v>
-      </c>
-      <c r="O8" s="30">
-        <v>8</v>
-      </c>
-      <c r="P8" s="97">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="13">
-        <f t="shared" si="3"/>
-        <v>0.625</v>
-      </c>
-      <c r="R8" s="30">
-        <v>8</v>
-      </c>
-      <c r="S8" s="97">
-        <v>5</v>
-      </c>
-      <c r="T8" s="13">
-        <f t="shared" si="4"/>
-        <v>0.625</v>
-      </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2.2222222222222223</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2112,17 +2115,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.56000000000000005</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>619</v>
+        <v>148</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2130,39 +2133,39 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>44.214285714285715</v>
+        <v>21.142857142857142</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P10" s="97">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>0.77777777777777779</v>
+        <v>1</v>
       </c>
       <c r="R10" s="30">
-        <v>71</v>
+        <v>309</v>
       </c>
       <c r="S10" s="97">
-        <v>58</v>
+        <v>309</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0.81690140845070425</v>
+        <v>1</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>8.2857142857142865</v>
+        <v>154.5</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>1.0503018108651911</v>
+        <v>1</v>
       </c>
       <c r="W10" s="34"/>
       <c r="AB10">
@@ -2564,11 +2567,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.12533333333333332</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2576,15 +2579,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>671</v>
+        <v>186</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>1.7428571428571429</v>
+        <v>0.48311688311688311</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>14.276595744680851</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2592,31 +2595,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.81395348837209303</v>
+        <v>0.77142857142857146</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>110.85</v>
+        <v>357.45</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>94</v>
+        <v>348.95</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.84799278304014436</v>
+        <v>0.97622045041264516</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>2.6857142857142855</v>
+        <v>12.924074074074074</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3493,11 +3496,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>6.1157024793388429E-2</v>
+        <v>5.7520661157024797E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3505,15 +3508,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>838</v>
+        <v>353</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>0.32417794970986458</v>
+        <v>0.13655705996131529</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>4.5297297297297296</v>
+        <v>2.0287356321839081</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3521,31 +3524,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.77083333333333337</v>
+        <v>0.76086956521739135</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>349.85</v>
+        <v>596.45000000000005</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>224</v>
+        <v>478.95</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.64027440331570673</v>
+        <v>0.80300108978120543</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.5135135135135136</v>
+        <v>3.4210714285714285</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3610,18 +3613,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.66666666666666663</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" s="94">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3716,34 +3719,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11+8+11+8+16+14</f>
-        <v>121</v>
+        <f>5+9+9+11+10+9+11+8+11+8+16+14+16</f>
+        <v>137</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.20166666666666666</v>
+        <v>0.22833333333333333</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>238.45</v>
+        <v>258</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.41469565217391302</v>
+        <v>0.44869565217391305</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>336.55</v>
+        <v>317</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>37.394444444444446</v>
+        <v>45.285714285714285</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.9706611570247934</v>
+        <v>1.8832116788321167</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3784,27 +3787,27 @@
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <v>120.25</v>
+        <v>120</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.21863636363636363</v>
+        <v>0.21818181818181817</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>429.75</v>
+        <v>430</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>47.75</v>
+        <v>61.428571428571431</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.15625</v>
+        <v>1.1538461538461537</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.2613636363636362</v>
+        <v>1.2587412587412585</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3854,7 +3857,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>55.964444444444446</v>
+        <v>71.954285714285717</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3914,7 +3917,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>54.522222222222219</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
@@ -3949,38 +3952,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11+11+8+7+9+24+14</f>
-        <v>134</v>
+        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13</f>
+        <v>147</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.22333333333333333</v>
+        <v>0.245</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>240.6</v>
+        <v>260</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.41843478260869565</v>
+        <v>0.45217391304347826</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>334.4</v>
+        <v>315</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>37.155555555555551</v>
+        <v>45</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.7955223880597015</v>
+        <v>1.7687074829931972</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.873588578844906</v>
+        <v>1.8456078083407277</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4025,7 +4028,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>61.111111111111114</v>
+        <v>78.571428571428569</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4060,38 +4063,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>4+7+3+3+3+6+5+6+6</f>
-        <v>43</v>
+        <f>4+7+3+3+3+6+5+6+6+7+2</f>
+        <v>52</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.215</v>
+        <v>0.26</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <v>735</v>
+        <v>1103</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.15909090909090909</v>
+        <v>0.23874458874458873</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>3885</v>
+        <v>3517</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>431.66666666666669</v>
+        <v>502.42857142857144</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>17.093023255813954</v>
+        <v>21.21153846153846</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.7399577167019028</v>
+        <v>0.91824841824841819</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4142,7 +4145,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>70.222222222222229</v>
+        <v>90.285714285714292</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4199,7 +4202,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>59</v>
+        <v>75.857142857142861</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4399,7 +4402,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>133.33333333333334</v>
+        <v>171.42857142857142</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4506,11 +4509,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.1028</v>
+        <v>0.1104</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4518,23 +4521,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>1776.92</v>
+        <v>2183.62</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.16653420805998126</v>
+        <v>0.20465042174320525</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>8893.08</v>
+        <v>8486.380000000001</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>988.12</v>
+        <v>1212.3400000000001</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.4570428015564203</v>
+        <v>3.9558333333333331</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4587,7 +4590,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>51.666666666666664</v>
+        <v>66.428571428571431</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4643,7 +4646,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>51.888888888888886</v>
+        <v>66.714285714285708</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4699,7 +4702,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>51.555555555555557</v>
+        <v>66.285714285714292</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4755,7 +4758,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>52.555555555555557</v>
+        <v>67.571428571428569</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4811,7 +4814,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>53.777777777777779</v>
+        <v>69.142857142857139</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4867,7 +4870,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>261.44444444444446</v>
+        <v>336.14285714285717</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4924,7 +4927,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>68.444444444444443</v>
+        <v>88</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4980,7 +4983,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>62.888888888888886</v>
+        <v>80.857142857142861</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5036,7 +5039,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>63.777777777777779</v>
+        <v>82</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5092,7 +5095,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>68</v>
+        <v>87.428571428571431</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5148,7 +5151,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>263.11111111111109</v>
+        <v>338.28571428571428</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5177,11 +5180,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>715</v>
+        <v>753</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.13119266055045872</v>
+        <v>0.13816513761467891</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5189,23 +5192,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>2055.92</v>
+        <v>2462.62</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.13120102105934908</v>
+        <v>0.15715507338864071</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>13614.08</v>
+        <v>13207.380000000001</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>1512.6755555555555</v>
+        <v>1886.7685714285715</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.8754125874125873</v>
+        <v>3.2704116865869852</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84277FEB-788F-4790-8AF0-CE2E17CCD28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08ACCFD-7B38-4556-94DE-239C0E572E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="79">
   <si>
     <t>Booking</t>
   </si>
@@ -259,7 +259,7 @@
     <t>Resigned</t>
   </si>
   <si>
-    <t xml:space="preserve">Leave </t>
+    <t>A Little Pending</t>
   </si>
   <si>
     <t>Pending</t>
@@ -1512,10 +1512,10 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7265625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="23.7265625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.453125" style="24" customWidth="1"/>
     <col min="8" max="8" width="7.7265625" customWidth="1"/>
@@ -1523,7 +1523,8 @@
     <col min="10" max="10" width="8.1796875" customWidth="1"/>
     <col min="11" max="11" width="8.81640625" customWidth="1"/>
     <col min="12" max="12" width="5.54296875" customWidth="1"/>
-    <col min="13" max="15" width="7.1796875" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" customWidth="1"/>
+    <col min="14" max="15" width="7.1796875" customWidth="1"/>
     <col min="16" max="16" width="8.7265625" customWidth="1"/>
     <col min="17" max="18" width="7.1796875" customWidth="1"/>
     <col min="19" max="19" width="8.7265625" customWidth="1"/>
@@ -1556,7 +1557,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1677,59 +1678,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.0909090909090908</v>
+        <v>1.25</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.3636363636363635</v>
+        <v>1.5625</v>
       </c>
       <c r="O4" s="30">
-        <v>16</v>
-      </c>
-      <c r="P4" s="96">
-        <v>16</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="P4" s="96"/>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="30">
-        <v>19.95</v>
-      </c>
-      <c r="S4" s="96">
-        <v>19.95</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="S4" s="96"/>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>1</v>
-      </c>
-      <c r="U4" s="30">
+        <v>0</v>
+      </c>
+      <c r="U4" s="30" t="e">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.246875</v>
-      </c>
-      <c r="V4" s="33">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V4" s="33" t="e">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="W4" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W4" s="34" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="5" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
@@ -1754,61 +1753,59 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>3.3333333333333335</v>
+        <v>1.4545454545454546</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>5.5555555555555554</v>
+        <v>2.4242424242424243</v>
       </c>
       <c r="O5" s="30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P5" s="97">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="30">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="S5" s="97">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U5" s="11" t="e">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V5" s="14" t="e">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W5" s="34" t="s">
-        <v>78</v>
-      </c>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W5" s="34"/>
     </row>
     <row r="6" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
@@ -1899,30 +1896,26 @@
       <c r="G7" s="30">
         <v>50</v>
       </c>
-      <c r="H7" s="12">
-        <v>7</v>
-      </c>
+      <c r="H7" s="12"/>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
-      <c r="K7" s="12">
-        <v>8</v>
-      </c>
+      <c r="K7" s="12"/>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="N7" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>1.9047619047619047</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O7" s="30"/>
       <c r="P7" s="97"/>
@@ -1945,7 +1938,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="W7" s="34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -1971,57 +1964,57 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>3.3333333333333335</v>
       </c>
       <c r="O8" s="30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P8" s="97">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0.9</v>
+        <v>3.5714285714285716</v>
       </c>
       <c r="R8" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="S8" s="97">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>2.2222222222222223</v>
+        <v>0.92</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1.1111111111111112</v>
+        <v>1.2879999999999998</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2115,17 +2108,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>0.24</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>148</v>
+        <v>67</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2133,41 +2126,39 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>21.142857142857142</v>
+        <v>11.166666666666666</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <v>2</v>
-      </c>
-      <c r="P10" s="97">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P10" s="97"/>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="30">
-        <v>309</v>
-      </c>
-      <c r="S10" s="97">
-        <v>309</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="S10" s="97"/>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="U10" s="11">
+        <v>0</v>
+      </c>
+      <c r="U10" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>154.5</v>
-      </c>
-      <c r="V10" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V10" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="W10" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W10" s="34" t="s">
+        <v>77</v>
+      </c>
       <c r="AB10">
         <v>33</v>
       </c>
@@ -2567,11 +2558,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>9.6000000000000002E-2</v>
+        <v>9.8666666666666666E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2579,15 +2570,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>186</v>
+        <v>109</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.48311688311688311</v>
+        <v>0.2831168831168831</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>5.166666666666667</v>
+        <v>2.9459459459459461</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2595,31 +2586,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.77142857142857146</v>
+        <v>1</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>357.45</v>
+        <v>65</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>348.95</v>
+        <v>28</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.97622045041264516</v>
+        <v>0.43076923076923079</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>12.924074074074074</v>
+        <v>0.82352941176470584</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3496,11 +3487,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.7520661157024797E-2</v>
+        <v>5.7851239669421489E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3508,15 +3499,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>353</v>
+        <v>276</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>0.13655705996131529</v>
+        <v>0.10676982591876209</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>2.0287356321839081</v>
+        <v>1.5771428571428572</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3524,31 +3515,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.76086956521739135</v>
+        <v>0.80327868852459017</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>596.45000000000005</v>
+        <v>304</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>478.95</v>
+        <v>158</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.80300108978120543</v>
+        <v>0.51973684210526316</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>3.4210714285714285</v>
+        <v>1.0748299319727892</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3577,21 +3568,23 @@
   <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7265625" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" customWidth="1"/>
-    <col min="5" max="5" width="23.7265625" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.26953125" style="24" customWidth="1"/>
-    <col min="8" max="8" width="10.54296875" customWidth="1"/>
-    <col min="9" max="9" width="5.54296875" customWidth="1"/>
-    <col min="10" max="10" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="7.7265625" customWidth="1"/>
-    <col min="15" max="15" width="5.26953125" customWidth="1"/>
-    <col min="17" max="17" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3613,18 +3606,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.7407407407407407</v>
+        <v>0.85185185185185186</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" s="94">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3719,34 +3712,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11+8+11+8+16+14+16</f>
-        <v>137</v>
+        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15</f>
+        <v>172</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.22833333333333333</v>
+        <v>0.28666666666666668</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.44869565217391305</v>
+        <v>0.48173913043478261</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>45.285714285714285</v>
+        <v>74.5</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.8832116788321167</v>
+        <v>1.6104651162790697</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3776,38 +3769,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3+2+5+7+14+20+10</f>
-        <v>104</v>
+        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15</f>
+        <v>137</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.17333333333333334</v>
+        <v>0.22833333333333333</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <v>120</v>
+        <v>131.4</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.21818181818181817</v>
+        <v>0.23890909090909093</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>430</v>
+        <v>418.6</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>61.428571428571431</v>
+        <v>104.65</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.1538461538461537</v>
+        <v>0.9591240875912409</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.2587412587412585</v>
+        <v>1.046317186463172</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3857,7 +3850,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>71.954285714285717</v>
+        <v>125.92</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3894,40 +3887,42 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+13+0+4+3+4+9+5</f>
-        <v>43</v>
+        <f>5+13+0+4+3+4+9+5+8</f>
+        <v>51</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>7.166666666666667E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="J7" s="11">
         <v>550</v>
       </c>
       <c r="K7" s="12">
-        <v>59.3</v>
+        <v>67</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.10781818181818181</v>
+        <v>0.12181818181818181</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>490.7</v>
+        <v>483</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>70.099999999999994</v>
+        <v>120.75</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.3790697674418604</v>
+        <v>1.3137254901960784</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.5044397463002113</v>
-      </c>
-      <c r="Q7" s="34"/>
+        <v>1.4331550802139035</v>
+      </c>
+      <c r="Q7" s="34" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="8" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -3952,38 +3947,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13</f>
-        <v>147</v>
+        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13+12+16</f>
+        <v>175</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.245</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>260</v>
+        <v>295.8</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.45217391304347826</v>
+        <v>0.51443478260869568</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>315</v>
+        <v>279.2</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>45</v>
+        <v>69.8</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.7687074829931972</v>
+        <v>1.6902857142857144</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.8456078083407277</v>
+        <v>1.7637763975155278</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4028,7 +4023,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>78.571428571428569</v>
+        <v>137.5</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4063,38 +4058,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>4+7+3+3+3+6+5+6+6+7+2</f>
-        <v>52</v>
+        <f>4+7+3+3+3+6+5+6+6+7+2+8+16</f>
+        <v>76</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <v>1103</v>
+        <v>1303.8499999999999</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.23874458874458873</v>
+        <v>0.2822186147186147</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>3517</v>
+        <v>3316.15</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>502.42857142857144</v>
+        <v>829.03750000000002</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>21.21153846153846</v>
+        <v>17.155921052631577</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.91824841824841819</v>
+        <v>0.74268056504898605</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4145,7 +4140,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>90.285714285714292</v>
+        <v>158</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4202,7 +4197,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>75.857142857142861</v>
+        <v>132.75</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4380,7 +4375,7 @@
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="70" t="e">
         <f t="shared" ref="I16" si="12">H16/G16</f>
@@ -4390,19 +4385,19 @@
         <v>1500</v>
       </c>
       <c r="K16" s="12">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="L16" s="71">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="M16" s="12">
         <f t="shared" si="5"/>
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>171.42857142857142</v>
+        <v>225</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4509,11 +4504,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>552</v>
+        <v>681</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.1104</v>
+        <v>0.13619999999999999</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4521,23 +4516,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>2183.62</v>
+        <v>2758.37</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.20465042174320525</v>
+        <v>0.25851640112464852</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>8486.380000000001</v>
+        <v>7911.63</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>1212.3400000000001</v>
+        <v>1977.9075</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.9558333333333331</v>
+        <v>4.0504698972099851</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4590,7 +4585,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>66.428571428571431</v>
+        <v>116.25</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4646,7 +4641,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>66.714285714285708</v>
+        <v>116.75</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4702,7 +4697,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>66.285714285714292</v>
+        <v>116</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4758,7 +4753,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>67.571428571428569</v>
+        <v>118.25</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4814,7 +4809,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>69.142857142857139</v>
+        <v>121</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4870,7 +4865,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>336.14285714285717</v>
+        <v>588.25</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4927,7 +4922,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4983,7 +4978,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>80.857142857142861</v>
+        <v>141.5</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5039,7 +5034,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>82</v>
+        <v>143.5</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5095,7 +5090,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>87.428571428571431</v>
+        <v>153</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5151,7 +5146,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>338.28571428571428</v>
+        <v>592</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5180,11 +5175,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>753</v>
+        <v>882</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.13816513761467891</v>
+        <v>0.1618348623853211</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5192,23 +5187,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>2462.62</v>
+        <v>3037.37</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.15715507338864071</v>
+        <v>0.19383343969368219</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>13207.380000000001</v>
+        <v>12632.630000000001</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>1886.7685714285715</v>
+        <v>3158.1575000000003</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.2704116865869852</v>
+        <v>3.4437301587301588</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08ACCFD-7B38-4556-94DE-239C0E572E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBACA26-CAFA-488F-B92F-8E61F838544E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1678,57 +1678,59 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.25</v>
-      </c>
-      <c r="M4" s="30">
+        <v>0</v>
+      </c>
+      <c r="M4" s="30" t="e">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.25</v>
-      </c>
-      <c r="N4" s="33">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N4" s="33" t="e">
         <f t="shared" si="2"/>
-        <v>1.5625</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O4" s="30">
-        <v>14</v>
-      </c>
-      <c r="P4" s="96"/>
+        <v>7</v>
+      </c>
+      <c r="P4" s="96">
+        <v>5</v>
+      </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="R4" s="30">
-        <v>14</v>
-      </c>
-      <c r="S4" s="96"/>
+        <v>6</v>
+      </c>
+      <c r="S4" s="96">
+        <v>4</v>
+      </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0</v>
-      </c>
-      <c r="U4" s="30" t="e">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" s="33" t="e">
+        <v>0.8</v>
+      </c>
+      <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W4" s="34" t="s">
-        <v>78</v>
-      </c>
+        <v>0.93333333333333324</v>
+      </c>
+      <c r="W4" s="34"/>
     </row>
     <row r="5" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
@@ -1753,59 +1755,61 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.04</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.53333333333333333</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1.4545454545454546</v>
+        <v>5.5</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>2.4242424242424243</v>
+        <v>9.1666666666666661</v>
       </c>
       <c r="O5" s="30">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P5" s="97">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="30">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="S5" s="97">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="U5" s="11">
+        <v>0</v>
+      </c>
+      <c r="U5" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="V5" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V5" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="W5" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W5" s="34" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="6" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
@@ -1964,57 +1968,57 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>1.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>3.3333333333333335</v>
+        <v>2.5</v>
       </c>
       <c r="O8" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P8" s="97">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>3.5714285714285716</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="R8" s="30">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="S8" s="97">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>4.5999999999999996</v>
+        <v>0.875</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>0.92</v>
+        <v>1.4</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1.2879999999999998</v>
+        <v>1.05</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2108,17 +2112,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2126,35 +2130,39 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>11.166666666666666</v>
+        <v>17</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
+        <v>7</v>
+      </c>
+      <c r="P10" s="97">
         <v>4</v>
       </c>
-      <c r="P10" s="97"/>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="R10" s="30">
-        <v>40</v>
-      </c>
-      <c r="S10" s="97"/>
+        <v>85</v>
+      </c>
+      <c r="S10" s="97">
+        <v>49</v>
+      </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="11" t="e">
+        <v>0.57647058823529407</v>
+      </c>
+      <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V10" s="14" t="e">
+        <v>12.25</v>
+      </c>
+      <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1.0088235294117647</v>
       </c>
       <c r="W10" s="34" t="s">
         <v>77</v>
@@ -2558,11 +2566,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>9.8666666666666666E-2</v>
+        <v>2.9333333333333333E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2570,15 +2578,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.2831168831168831</v>
+        <v>0.25974025974025972</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>2.9459459459459461</v>
+        <v>9.0909090909090917</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2586,31 +2594,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>1</v>
+        <v>0.51351351351351349</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.43076923076923079</v>
+        <v>0.54471544715447151</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>0.82352941176470584</v>
+        <v>3.5263157894736841</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3487,11 +3495,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.7851239669421489E-2</v>
+        <v>4.9256198347107441E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3499,15 +3507,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>0.10676982591876209</v>
+        <v>0.10328820116054159</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.5771428571428572</v>
+        <v>1.7919463087248322</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3515,31 +3523,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.80327868852459017</v>
+        <v>0.70967741935483875</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>304</v>
+        <v>362</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.51973684210526316</v>
+        <v>0.54419889502762431</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.0748299319727892</v>
+        <v>1.4924242424242424</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3606,18 +3614,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.85185185185185186</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="94">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3712,34 +3720,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15</f>
-        <v>172</v>
+        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15+10</f>
+        <v>182</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.28666666666666668</v>
+        <v>0.30333333333333334</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.48173913043478261</v>
+        <v>0.48869565217391303</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>74.5</v>
+        <v>98</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.6104651162790697</v>
+        <v>1.543956043956044</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3769,12 +3777,12 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15</f>
-        <v>137</v>
+        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15+12</f>
+        <v>149</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.22833333333333333</v>
+        <v>0.24833333333333332</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
@@ -3792,15 +3800,15 @@
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>104.65</v>
+        <v>139.53333333333333</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.9591240875912409</v>
+        <v>0.8818791946308725</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.046317186463172</v>
+        <v>0.96205003050640647</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3850,7 +3858,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>125.92</v>
+        <v>167.89333333333335</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3910,7 +3918,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>120.75</v>
+        <v>161</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
@@ -3947,38 +3955,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13+12+16</f>
-        <v>175</v>
+        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13+12+16+12</f>
+        <v>187</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.29166666666666669</v>
+        <v>0.31166666666666665</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>295.8</v>
+        <v>310</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.51443478260869568</v>
+        <v>0.53913043478260869</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>279.2</v>
+        <v>265</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>69.8</v>
+        <v>88.333333333333329</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.6902857142857144</v>
+        <v>1.6577540106951871</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.7637763975155278</v>
+        <v>1.7298302720297607</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4023,7 +4031,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>137.5</v>
+        <v>183.33333333333334</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4058,38 +4066,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>4+7+3+3+3+6+5+6+6+7+2+8+16</f>
-        <v>76</v>
+        <f>4+7+3+3+3+6+5+6+6+7+2+8+16+7</f>
+        <v>83</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.38</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <v>1303.8499999999999</v>
+        <v>1353</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.2822186147186147</v>
+        <v>0.29285714285714287</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>3316.15</v>
+        <v>3267</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>829.03750000000002</v>
+        <v>1089</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>17.155921052631577</v>
+        <v>16.301204819277107</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.74268056504898605</v>
+        <v>0.70567986230636837</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4140,7 +4148,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>158</v>
+        <v>210.66666666666666</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4197,7 +4205,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>132.75</v>
+        <v>177</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4397,7 +4405,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4504,11 +4512,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>681</v>
+        <v>722</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.13619999999999999</v>
+        <v>0.1444</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4516,23 +4524,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>2758.37</v>
+        <v>2825.7200000000003</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.25851640112464852</v>
+        <v>0.26482849109653234</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>7911.63</v>
+        <v>7844.28</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>1977.9075</v>
+        <v>2614.7599999999998</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>4.0504698972099851</v>
+        <v>3.9137396121883659</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4585,7 +4593,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>116.25</v>
+        <v>155</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4641,7 +4649,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>116.75</v>
+        <v>155.66666666666666</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4697,7 +4705,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>116</v>
+        <v>154.66666666666666</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4753,7 +4761,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>118.25</v>
+        <v>157.66666666666666</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4809,7 +4817,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>121</v>
+        <v>161.33333333333334</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4865,7 +4873,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>588.25</v>
+        <v>784.33333333333337</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4922,7 +4930,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>154</v>
+        <v>205.33333333333334</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4978,7 +4986,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>141.5</v>
+        <v>188.66666666666666</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5034,7 +5042,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>143.5</v>
+        <v>191.33333333333334</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5090,7 +5098,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>153</v>
+        <v>204</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5146,7 +5154,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>592</v>
+        <v>789.33333333333337</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5175,11 +5183,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>882</v>
+        <v>923</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.1618348623853211</v>
+        <v>0.1693577981651376</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5187,23 +5195,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>3037.37</v>
+        <v>3104.7200000000003</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.19383343969368219</v>
+        <v>0.19813146139119339</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>12632.630000000001</v>
+        <v>12565.279999999999</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>3158.1575000000003</v>
+        <v>4188.4266666666663</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.4437301587301588</v>
+        <v>3.3637269772481044</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBACA26-CAFA-488F-B92F-8E61F838544E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9CDCFD-3235-4815-B38C-7A3182E45E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="79">
   <si>
     <t>Booking</t>
   </si>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1678,57 +1678,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
+        <v>0.35</v>
+      </c>
+      <c r="M4" s="30">
+        <f t="shared" ref="M4:N12" si="2">K4/H4</f>
+        <v>1.5555555555555556</v>
+      </c>
+      <c r="N4" s="33">
+        <f t="shared" si="2"/>
+        <v>1.9444444444444444</v>
+      </c>
+      <c r="O4" s="30">
         <v>0</v>
       </c>
-      <c r="M4" s="30" t="e">
-        <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N4" s="33" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O4" s="30">
-        <v>7</v>
-      </c>
       <c r="P4" s="96">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="32" t="e">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.7142857142857143</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R4" s="30">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S4" s="96">
-        <v>4</v>
-      </c>
-      <c r="T4" s="32">
+        <v>0</v>
+      </c>
+      <c r="T4" s="32" t="e">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="U4" s="30">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U4" s="30" t="e">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>0.8</v>
-      </c>
-      <c r="V4" s="33">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V4" s="33" t="e">
         <f t="shared" si="5"/>
-        <v>0.93333333333333324</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1755,57 +1755,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.36666666666666664</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>5.5</v>
+        <v>1.5454545454545454</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>9.1666666666666661</v>
+        <v>2.5757575757575757</v>
       </c>
       <c r="O5" s="30">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="P5" s="97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="R5" s="30">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="S5" s="97">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U5" s="11" t="e">
+        <v>0.17857142857142858</v>
+      </c>
+      <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V5" s="14" t="e">
+        <v>5</v>
+      </c>
+      <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>3.2142857142857144</v>
       </c>
       <c r="W5" s="34" t="s">
         <v>78</v>
@@ -1968,59 +1968,61 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O8" s="30">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P8" s="97">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0.83333333333333337</v>
+        <v>0</v>
       </c>
       <c r="R8" s="30">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="S8" s="97">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.875</v>
-      </c>
-      <c r="U8" s="11">
+        <v>0</v>
+      </c>
+      <c r="U8" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>1.4</v>
-      </c>
-      <c r="V8" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V8" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>1.05</v>
-      </c>
-      <c r="W8" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W8" s="34" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="9" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
@@ -2112,17 +2114,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2130,7 +2132,7 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>6.2857142857142856</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2140,29 +2142,29 @@
         <v>7</v>
       </c>
       <c r="P10" s="97">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>0.5714285714285714</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="R10" s="30">
         <v>85</v>
       </c>
       <c r="S10" s="97">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0.57647058823529407</v>
+        <v>0.47058823529411764</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>12.25</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>1.0088235294117647</v>
+        <v>1.0980392156862746</v>
       </c>
       <c r="W10" s="34" t="s">
         <v>77</v>
@@ -2566,11 +2568,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>2.9333333333333333E-2</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2578,15 +2580,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.25974025974025972</v>
+        <v>0.22597402597402597</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>9.0909090909090917</v>
+        <v>2.6363636363636362</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2594,31 +2596,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.51351351351351349</v>
+        <v>0.13793103448275862</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.54471544715447151</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>3.5263157894736841</v>
+        <v>11.25</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3495,11 +3497,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>4.9256198347107441E-2</v>
+        <v>5.6528925619834712E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3507,15 +3509,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>0.10328820116054159</v>
+        <v>9.8259187620889754E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.7919463087248322</v>
+        <v>1.4853801169590644</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3523,31 +3525,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.70967741935483875</v>
+        <v>0.65730337078651691</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.54419889502762431</v>
+        <v>0.49157303370786515</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.4924242424242424</v>
+        <v>1.4957264957264957</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3614,18 +3616,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.88888888888888884</v>
+        <v>0.92592592592592593</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="94">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3743,7 +3745,7 @@
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
@@ -3777,38 +3779,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15+12</f>
-        <v>149</v>
+        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15+12+1</f>
+        <v>150</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.24833333333333332</v>
+        <v>0.25</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <v>131.4</v>
+        <v>136</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.23890909090909093</v>
+        <v>0.24727272727272728</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>418.6</v>
+        <v>414</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>139.53333333333333</v>
+        <v>207</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.8818791946308725</v>
+        <v>0.90666666666666662</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>0.96205003050640647</v>
+        <v>0.98909090909090913</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3858,7 +3860,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>167.89333333333335</v>
+        <v>251.84</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3918,7 +3920,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>161</v>
+        <v>241.5</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
@@ -3978,7 +3980,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>88.333333333333329</v>
+        <v>132.5</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
@@ -4031,7 +4033,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>183.33333333333334</v>
+        <v>275</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4066,38 +4068,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>4+7+3+3+3+6+5+6+6+7+2+8+16+7</f>
-        <v>83</v>
+        <f>4+7+3+3+3+6+5+6+6+7+2+8+16+7+3</f>
+        <v>86</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.41499999999999998</v>
+        <v>0.43</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <v>1353</v>
+        <v>1393</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.29285714285714287</v>
+        <v>0.30151515151515151</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>3267</v>
+        <v>3227</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>1089</v>
+        <v>1613.5</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>16.301204819277107</v>
+        <v>16.197674418604652</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.70567986230636837</v>
+        <v>0.70119802677942211</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4148,7 +4150,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>210.66666666666666</v>
+        <v>316</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4205,7 +4207,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>177</v>
+        <v>265.5</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4405,7 +4407,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4512,11 +4514,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.1444</v>
+        <v>0.1452</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4524,23 +4526,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>2825.7200000000003</v>
+        <v>2870.3199999999997</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.26482849109653234</v>
+        <v>0.26900843486410492</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>7844.28</v>
+        <v>7799.68</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>2614.7599999999998</v>
+        <v>3899.84</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.9137396121883659</v>
+        <v>3.953608815426997</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4593,7 +4595,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>155</v>
+        <v>232.5</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4649,7 +4651,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>155.66666666666666</v>
+        <v>233.5</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4705,7 +4707,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>154.66666666666666</v>
+        <v>232</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4761,7 +4763,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>157.66666666666666</v>
+        <v>236.5</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4817,7 +4819,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>161.33333333333334</v>
+        <v>242</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4873,7 +4875,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>784.33333333333337</v>
+        <v>1176.5</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4930,7 +4932,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>205.33333333333334</v>
+        <v>308</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4986,7 +4988,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>188.66666666666666</v>
+        <v>283</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5042,7 +5044,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>191.33333333333334</v>
+        <v>287</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5098,7 +5100,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>204</v>
+        <v>306</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5154,7 +5156,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>789.33333333333337</v>
+        <v>1184</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5183,11 +5185,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.1693577981651376</v>
+        <v>0.17009174311926606</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5195,23 +5197,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>3104.7200000000003</v>
+        <v>3149.3199999999997</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.19813146139119339</v>
+        <v>0.20097766432673897</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>12565.279999999999</v>
+        <v>12520.68</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>4188.4266666666663</v>
+        <v>6260.34</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.3637269772481044</v>
+        <v>3.3973247033441205</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9CDCFD-3235-4815-B38C-7A3182E45E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBD3ADD-09AA-4748-92E2-33F8E3285EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="78">
   <si>
     <t>Booking</t>
   </si>
@@ -260,9 +260,6 @@
   </si>
   <si>
     <t>A Little Pending</t>
-  </si>
-  <si>
-    <t>Pending</t>
   </si>
 </sst>
 </file>
@@ -1516,7 +1513,7 @@
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.453125" customWidth="1"/>
     <col min="7" max="7" width="5.453125" style="24" customWidth="1"/>
     <col min="8" max="8" width="7.7265625" customWidth="1"/>
     <col min="9" max="9" width="5.54296875" customWidth="1"/>
@@ -1557,7 +1554,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1678,57 +1675,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.5555555555555556</v>
+        <v>2</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.9444444444444444</v>
+        <v>2.5</v>
       </c>
       <c r="O4" s="30">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P4" s="96">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="32" t="e">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>#DIV/0!</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="R4" s="30">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S4" s="96">
-        <v>0</v>
-      </c>
-      <c r="T4" s="32" t="e">
+        <v>12</v>
+      </c>
+      <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" s="30" t="e">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" s="33" t="e">
+        <v>1.5</v>
+      </c>
+      <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1755,61 +1752,59 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.56666666666666665</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1.5454545454545454</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>2.5757575757575757</v>
+        <v>3.8888888888888893</v>
       </c>
       <c r="O5" s="30">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P5" s="97">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>5.5555555555555552E-2</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="R5" s="30">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="S5" s="97">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.17857142857142858</v>
+        <v>0.625</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>3.2142857142857144</v>
-      </c>
-      <c r="W5" s="34" t="s">
-        <v>78</v>
-      </c>
+        <v>0.98214285714285721</v>
+      </c>
+      <c r="W5" s="34"/>
     </row>
     <row r="6" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
@@ -1968,61 +1963,59 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
+        <v>6.5</v>
+      </c>
+      <c r="O8" s="30">
+        <v>6</v>
+      </c>
+      <c r="P8" s="97">
         <v>5</v>
-      </c>
-      <c r="O8" s="30">
-        <v>4</v>
-      </c>
-      <c r="P8" s="97">
-        <v>0</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="R8" s="30">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S8" s="97">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U8" s="11" t="e">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V8" s="14" t="e">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W8" s="34" t="s">
-        <v>78</v>
-      </c>
+        <v>1.0999999999999999</v>
+      </c>
+      <c r="W8" s="34"/>
     </row>
     <row r="9" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
@@ -2114,17 +2107,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>0.12</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2132,7 +2125,7 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>6.2857142857142856</v>
+        <v>16.666666666666668</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2149,22 +2142,22 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="R10" s="30">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="S10" s="97">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0.47058823529411764</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>13.333333333333334</v>
+        <v>4</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>1.0980392156862746</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="W10" s="34" t="s">
         <v>77</v>
@@ -2568,11 +2561,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>8.7999999999999995E-2</v>
+        <v>4.5333333333333337E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2580,15 +2573,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.22597402597402597</v>
+        <v>0.21298701298701297</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>2.6363636363636362</v>
+        <v>4.8235294117647056</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2596,19 +2589,19 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.13793103448275862</v>
+        <v>0.69696969696969702</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
@@ -2616,11 +2609,11 @@
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.38461538461538464</v>
+        <v>0.52325581395348841</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>11.25</v>
+        <v>1.9565217391304348</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3497,11 +3490,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.6528925619834712E-2</v>
+        <v>5.1239669421487603E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3509,15 +3502,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>9.8259187620889754E-2</v>
+        <v>9.6324951644100584E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.4853801169590644</v>
+        <v>1.6064516129032258</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3525,19 +3518,19 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.65730337078651691</v>
+        <v>0.74725274725274726</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
@@ -3545,11 +3538,11 @@
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.49157303370786515</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.4957264957264957</v>
+        <v>1.286764705882353</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3616,18 +3609,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.92592592592592593</v>
+        <v>1</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="94">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3722,34 +3715,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15+10</f>
-        <v>182</v>
+        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15+10+10</f>
+        <v>192</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.30333333333333334</v>
+        <v>0.32</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.48869565217391303</v>
+        <v>0.50782608695652176</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>294</v>
-      </c>
-      <c r="N4" s="10">
+        <v>283</v>
+      </c>
+      <c r="N4" s="10" t="e">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>147</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.543956043956044</v>
+        <v>1.5208333333333333</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3779,38 +3772,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15+12+1</f>
-        <v>150</v>
+        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15+12+1+6</f>
+        <v>156</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.24727272727272728</v>
+        <v>0.26545454545454544</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>414</v>
-      </c>
-      <c r="N5" s="14">
+        <v>404</v>
+      </c>
+      <c r="N5" s="14" t="e">
         <f t="shared" si="3"/>
-        <v>207</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.90666666666666662</v>
+        <v>0.9358974358974359</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>0.98909090909090913</v>
+        <v>1.0209790209790208</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3858,9 +3851,9 @@
         <f t="shared" si="2"/>
         <v>503.68</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="14" t="e">
         <f t="shared" si="3"/>
-        <v>251.84</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3918,9 +3911,9 @@
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
         <v>483</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="14" t="e">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>241.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
@@ -3957,38 +3950,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13+12+16+12</f>
-        <v>187</v>
+        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13+12+16+12+14</f>
+        <v>201</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.31166666666666665</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.53913043478260869</v>
+        <v>0.55826086956521737</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>265</v>
-      </c>
-      <c r="N8" s="14">
+        <v>254</v>
+      </c>
+      <c r="N8" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>132.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.6577540106951871</v>
+        <v>1.5970149253731343</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.7298302720297607</v>
+        <v>1.6664503569110964</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4031,9 +4024,9 @@
         <f t="shared" si="5"/>
         <v>550</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>275</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4089,9 +4082,9 @@
         <f t="shared" si="5"/>
         <v>3227</v>
       </c>
-      <c r="N10" s="14">
+      <c r="N10" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>1613.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
@@ -4137,28 +4130,27 @@
         <v>650</v>
       </c>
       <c r="K11" s="12">
-        <f>18+0</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L11" s="71">
         <f t="shared" si="1"/>
-        <v>2.7692307692307693E-2</v>
+        <v>0</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="5"/>
-        <v>632</v>
-      </c>
-      <c r="N11" s="14">
+        <v>650</v>
+      </c>
+      <c r="N11" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>316</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P11" s="14">
         <f t="shared" si="4"/>
-        <v>1.3846153846153846</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="34"/>
     </row>
@@ -4195,27 +4187,27 @@
         <v>550</v>
       </c>
       <c r="K12" s="12">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L12" s="71">
         <f t="shared" si="1"/>
-        <v>3.4545454545454546E-2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="5"/>
-        <v>531</v>
-      </c>
-      <c r="N12" s="14">
+        <v>550</v>
+      </c>
+      <c r="N12" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>265.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
-        <v>0.6785714285714286</v>
+        <v>0</v>
       </c>
       <c r="P12" s="14">
         <f t="shared" si="4"/>
-        <v>0.74025974025974028</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="34"/>
     </row>
@@ -4252,9 +4244,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N13" s="14">
+      <c r="N13" s="14" t="e">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O13" s="72" t="e">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
@@ -4301,9 +4293,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="14" t="e">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O14" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4350,9 +4342,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="14" t="e">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O15" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4405,9 +4397,9 @@
         <f t="shared" si="5"/>
         <v>900</v>
       </c>
-      <c r="N16" s="14">
+      <c r="N16" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>450</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4448,9 +4440,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N17" s="14">
+      <c r="N17" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O17" s="72"/>
       <c r="P17" s="14"/>
@@ -4485,9 +4477,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N18" s="77">
+      <c r="N18" s="77" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O18" s="78"/>
       <c r="P18" s="39"/>
@@ -4514,11 +4506,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>726</v>
+        <v>756</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.1452</v>
+        <v>0.1512</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4526,23 +4518,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>2870.3199999999997</v>
+        <v>2865.3199999999997</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.26900843486410492</v>
+        <v>0.26853983130271786</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>7799.68</v>
-      </c>
-      <c r="N19" s="83">
+        <v>7804.68</v>
+      </c>
+      <c r="N19" s="83" t="e">
         <f t="shared" si="6"/>
-        <v>3899.84</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.953608815426997</v>
+        <v>3.7901058201058198</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4593,9 +4585,9 @@
         <f t="shared" si="5"/>
         <v>465</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="10" t="e">
         <f t="shared" si="6"/>
-        <v>232.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4649,9 +4641,9 @@
         <f t="shared" si="5"/>
         <v>467</v>
       </c>
-      <c r="N21" s="14">
+      <c r="N21" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>233.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4705,9 +4697,9 @@
         <f t="shared" si="5"/>
         <v>464</v>
       </c>
-      <c r="N22" s="14">
+      <c r="N22" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>232</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4761,9 +4753,9 @@
         <f t="shared" si="5"/>
         <v>473</v>
       </c>
-      <c r="N23" s="14">
+      <c r="N23" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>236.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4817,9 +4809,9 @@
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
-      <c r="N24" s="77">
+      <c r="N24" s="77" t="e">
         <f t="shared" si="6"/>
-        <v>242</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4873,9 +4865,9 @@
         <f t="shared" si="5"/>
         <v>2353</v>
       </c>
-      <c r="N25" s="83">
+      <c r="N25" s="83" t="e">
         <f t="shared" si="6"/>
-        <v>1176.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4930,9 +4922,9 @@
         <f t="shared" si="5"/>
         <v>616</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="10" t="e">
         <f t="shared" si="6"/>
-        <v>308</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4986,9 +4978,9 @@
         <f t="shared" si="5"/>
         <v>566</v>
       </c>
-      <c r="N27" s="14">
+      <c r="N27" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>283</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5042,9 +5034,9 @@
         <f t="shared" si="5"/>
         <v>574</v>
       </c>
-      <c r="N28" s="14">
+      <c r="N28" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>287</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5098,9 +5090,9 @@
         <f t="shared" si="5"/>
         <v>612</v>
       </c>
-      <c r="N29" s="77">
+      <c r="N29" s="77" t="e">
         <f t="shared" si="6"/>
-        <v>306</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5154,9 +5146,9 @@
         <f t="shared" si="5"/>
         <v>2368</v>
       </c>
-      <c r="N30" s="83">
+      <c r="N30" s="83" t="e">
         <f t="shared" si="6"/>
-        <v>1184</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5185,11 +5177,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>927</v>
+        <v>957</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.17009174311926606</v>
+        <v>0.17559633027522936</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5197,23 +5189,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>3149.3199999999997</v>
+        <v>3144.3199999999997</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.20097766432673897</v>
+        <v>0.20065858328015315</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>12520.68</v>
-      </c>
-      <c r="N31" s="92">
+        <v>12525.68</v>
+      </c>
+      <c r="N31" s="92" t="e">
         <f t="shared" si="6"/>
-        <v>6260.34</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.3973247033441205</v>
+        <v>3.2856008359456634</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBD3ADD-09AA-4748-92E2-33F8E3285EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B33E0B-0B5B-4633-8248-FCDFFCABA912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="77">
   <si>
     <t>Booking</t>
   </si>
@@ -257,9 +257,6 @@
   </si>
   <si>
     <t>Resigned</t>
-  </si>
-  <si>
-    <t>A Little Pending</t>
   </si>
 </sst>
 </file>
@@ -1554,7 +1551,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1675,57 +1672,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.3</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>2</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>0.91666666666666674</v>
       </c>
       <c r="O4" s="30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P4" s="96">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.88888888888888884</v>
+        <v>1</v>
       </c>
       <c r="R4" s="30">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S4" s="96">
         <v>12</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>0.9642857142857143</v>
+        <v>1</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1752,57 +1749,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.23333333333333334</v>
+        <v>0.3</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>2.3333333333333335</v>
+        <v>1.125</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>3.8888888888888893</v>
+        <v>1.875</v>
       </c>
       <c r="O5" s="30">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P5" s="97">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0.63636363636363635</v>
+        <v>1</v>
       </c>
       <c r="R5" s="30">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="S5" s="97">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>1.4285714285714286</v>
+        <v>2.25</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>0.98214285714285721</v>
+        <v>1</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1973,47 +1970,47 @@
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>13</v>
+        <v>15.7</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.78499999999999992</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>2.6</v>
+        <v>3.1399999999999997</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>6.5</v>
+        <v>7.8499999999999988</v>
       </c>
       <c r="O8" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P8" s="97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0.83333333333333337</v>
+        <v>0.8</v>
       </c>
       <c r="R8" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S8" s="97">
-        <v>11</v>
+        <v>12.8</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.91666666666666663</v>
+        <v>0.98461538461538467</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>2.2000000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1.0999999999999999</v>
+        <v>1.2307692307692308</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2107,11 +2104,11 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
@@ -2125,43 +2122,41 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>16.666666666666668</v>
+        <v>10</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P10" s="97">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>0.42857142857142855</v>
+        <v>1</v>
       </c>
       <c r="R10" s="30">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="S10" s="97">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0.27272727272727271</v>
+        <v>1</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>13.5</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>0.63636363636363635</v>
-      </c>
-      <c r="W10" s="34" t="s">
-        <v>77</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="W10" s="34"/>
       <c r="AB10">
         <v>33</v>
       </c>
@@ -2561,11 +2556,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>4.5333333333333337E-2</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2573,15 +2568,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>82</v>
+        <v>85.7</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.21298701298701297</v>
+        <v>0.2225974025974026</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>4.8235294117647056</v>
+        <v>2.5969696969696972</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2589,31 +2584,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.69696969696969702</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>45</v>
+        <v>87.8</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.52325581395348841</v>
+        <v>0.99772727272727268</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>1.9565217391304348</v>
+        <v>4.8777777777777773</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3490,11 +3485,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.1239669421487603E-2</v>
+        <v>5.6528925619834712E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3502,15 +3497,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>249</v>
+        <v>252.7</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>9.6324951644100584E-2</v>
+        <v>9.7756286266924564E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.6064516129032258</v>
+        <v>1.4777777777777776</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3518,31 +3513,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.74725274725274726</v>
+        <v>0.77976190476190477</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>175</v>
+        <v>217.8</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.53846153846153844</v>
+        <v>0.66605504587155961</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.286764705882353</v>
+        <v>1.6625954198473283</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3609,18 +3604,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>1</v>
+        <v>0.92592592592592593</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="94">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3715,34 +3710,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15+10+10</f>
-        <v>192</v>
+        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15+10+10+16</f>
+        <v>208</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.32</v>
+        <v>0.34666666666666668</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.50782608695652176</v>
+        <v>0.5304347826086957</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>283</v>
-      </c>
-      <c r="N4" s="10" t="e">
+        <v>270</v>
+      </c>
+      <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>#DIV/0!</v>
+        <v>135</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.5208333333333333</v>
+        <v>1.4663461538461537</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3772,38 +3767,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15+12+1+6</f>
-        <v>156</v>
+        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15+12+1+6+8</f>
+        <v>164</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.27333333333333332</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.26545454545454544</v>
+        <v>0.28363636363636363</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>404</v>
-      </c>
-      <c r="N5" s="14" t="e">
+        <v>394</v>
+      </c>
+      <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>197</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.9358974358974359</v>
+        <v>0.95121951219512191</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.0209790209790208</v>
+        <v>1.0376940133037695</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3851,9 +3846,9 @@
         <f t="shared" si="2"/>
         <v>503.68</v>
       </c>
-      <c r="N6" s="14" t="e">
+      <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>251.84</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3911,9 +3906,9 @@
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
         <v>483</v>
       </c>
-      <c r="N7" s="14" t="e">
+      <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>#DIV/0!</v>
+        <v>241.5</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
@@ -3950,38 +3945,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13+12+16+12+14</f>
-        <v>201</v>
+        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13+12+16+12+14+18</f>
+        <v>219</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.33500000000000002</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.55826086956521737</v>
+        <v>0.5808695652173913</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>254</v>
-      </c>
-      <c r="N8" s="14" t="e">
+        <v>241</v>
+      </c>
+      <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>120.5</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.5970149253731343</v>
+        <v>1.5251141552511416</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.6664503569110964</v>
+        <v>1.5914234663490172</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4024,9 +4019,9 @@
         <f t="shared" si="5"/>
         <v>550</v>
       </c>
-      <c r="N9" s="14" t="e">
+      <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>275</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4061,38 +4056,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>4+7+3+3+3+6+5+6+6+7+2+8+16+7+3</f>
-        <v>86</v>
+        <f>4+7+3+3+3+6+5+6+6+7+2+8+16+7+3+4</f>
+        <v>90</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <v>1393</v>
+        <v>1458</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.30151515151515151</v>
+        <v>0.31558441558441558</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>3227</v>
-      </c>
-      <c r="N10" s="14" t="e">
+        <v>3162</v>
+      </c>
+      <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>1581</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>16.197674418604652</v>
+        <v>16.2</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.70119802677942211</v>
+        <v>0.70129870129870131</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4140,9 +4135,9 @@
         <f t="shared" si="5"/>
         <v>650</v>
       </c>
-      <c r="N11" s="14" t="e">
+      <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>325</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4197,9 +4192,9 @@
         <f t="shared" si="5"/>
         <v>550</v>
       </c>
-      <c r="N12" s="14" t="e">
+      <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>275</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4244,9 +4239,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N13" s="14" t="e">
+      <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="O13" s="72" t="e">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
@@ -4293,9 +4288,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N14" s="14" t="e">
+      <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="O14" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4342,9 +4337,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N15" s="14" t="e">
+      <c r="N15" s="14">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="O15" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4397,9 +4392,9 @@
         <f t="shared" si="5"/>
         <v>900</v>
       </c>
-      <c r="N16" s="14" t="e">
+      <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>450</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4440,9 +4435,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N17" s="14" t="e">
+      <c r="N17" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="O17" s="72"/>
       <c r="P17" s="14"/>
@@ -4477,9 +4472,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N18" s="77" t="e">
+      <c r="N18" s="77">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="O18" s="78"/>
       <c r="P18" s="39"/>
@@ -4506,11 +4501,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>756</v>
+        <v>802</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.1512</v>
+        <v>0.16039999999999999</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4518,23 +4513,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>2865.3199999999997</v>
+        <v>2966.3199999999997</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.26853983130271786</v>
+        <v>0.27800562324273664</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>7804.68</v>
-      </c>
-      <c r="N19" s="83" t="e">
+        <v>7703.68</v>
+      </c>
+      <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>3851.84</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.7901058201058198</v>
+        <v>3.6986533665835406</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4585,9 +4580,9 @@
         <f t="shared" si="5"/>
         <v>465</v>
       </c>
-      <c r="N20" s="10" t="e">
+      <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>232.5</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4641,9 +4636,9 @@
         <f t="shared" si="5"/>
         <v>467</v>
       </c>
-      <c r="N21" s="14" t="e">
+      <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>233.5</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4697,9 +4692,9 @@
         <f t="shared" si="5"/>
         <v>464</v>
       </c>
-      <c r="N22" s="14" t="e">
+      <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>232</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4753,9 +4748,9 @@
         <f t="shared" si="5"/>
         <v>473</v>
       </c>
-      <c r="N23" s="14" t="e">
+      <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>236.5</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4809,9 +4804,9 @@
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
-      <c r="N24" s="77" t="e">
+      <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>242</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4865,9 +4860,9 @@
         <f t="shared" si="5"/>
         <v>2353</v>
       </c>
-      <c r="N25" s="83" t="e">
+      <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>1176.5</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4922,9 +4917,9 @@
         <f t="shared" si="5"/>
         <v>616</v>
       </c>
-      <c r="N26" s="10" t="e">
+      <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>308</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4978,9 +4973,9 @@
         <f t="shared" si="5"/>
         <v>566</v>
       </c>
-      <c r="N27" s="14" t="e">
+      <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>283</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5034,9 +5029,9 @@
         <f t="shared" si="5"/>
         <v>574</v>
       </c>
-      <c r="N28" s="14" t="e">
+      <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>287</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5090,9 +5085,9 @@
         <f t="shared" si="5"/>
         <v>612</v>
       </c>
-      <c r="N29" s="77" t="e">
+      <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>306</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5146,9 +5141,9 @@
         <f t="shared" si="5"/>
         <v>2368</v>
       </c>
-      <c r="N30" s="83" t="e">
+      <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>1184</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5177,11 +5172,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>957</v>
+        <v>1003</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.17559633027522936</v>
+        <v>0.18403669724770641</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5189,23 +5184,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>3144.3199999999997</v>
+        <v>3245.3199999999997</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.20065858328015315</v>
+        <v>0.20710402042118697</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>12525.68</v>
-      </c>
-      <c r="N31" s="92" t="e">
+        <v>12424.68</v>
+      </c>
+      <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>6212.34</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.2856008359456634</v>
+        <v>3.2356131605184442</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B33E0B-0B5B-4633-8248-FCDFFCABA912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7CD8F8-BD23-462B-BBAE-C74421378BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -3604,18 +3604,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.92592592592592593</v>
+        <v>0.96296296296296291</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="94">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3710,34 +3710,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15+10+10+16</f>
-        <v>208</v>
+        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15+10+10+16+12</f>
+        <v>220</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.34666666666666668</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.5304347826086957</v>
+        <v>0.54260869565217396</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>135</v>
+        <v>263</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.4663461538461537</v>
+        <v>1.4181818181818182</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3767,38 +3767,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15+12+1+6+8</f>
-        <v>164</v>
+        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15+12+1+6+8+8</f>
+        <v>172</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.27333333333333332</v>
+        <v>0.28666666666666668</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.28363636363636363</v>
+        <v>0.29636363636363638</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.95121951219512191</v>
+        <v>0.94767441860465118</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.0376940133037695</v>
+        <v>1.0338266384778012</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>251.84</v>
+        <v>503.68</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>241.5</v>
+        <v>483</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
@@ -3945,38 +3945,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13+12+16+12+14+18</f>
-        <v>219</v>
+        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13+12+16+12+14+18+15</f>
+        <v>234</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.36499999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.5808695652173913</v>
+        <v>0.60869565217391308</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>120.5</v>
+        <v>225</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.5251141552511416</v>
+        <v>1.4957264957264957</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.5914234663490172</v>
+        <v>1.5607580824972129</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>275</v>
+        <v>550</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4056,38 +4056,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>4+7+3+3+3+6+5+6+6+7+2+8+16+7+3+4</f>
-        <v>90</v>
+        <f>4+7+3+3+3+6+5+6+6+7+2+8+16+7+3+4+8</f>
+        <v>98</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.31558441558441558</v>
+        <v>0.31601731601731603</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>3162</v>
+        <v>3160</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>1581</v>
+        <v>3160</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>16.2</v>
+        <v>14.897959183673469</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.70129870129870131</v>
+        <v>0.64493329799452248</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>325</v>
+        <v>650</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>275</v>
+        <v>550</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4501,11 +4501,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>802</v>
+        <v>845</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.16039999999999999</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4513,23 +4513,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>2966.3199999999997</v>
+        <v>2998.32</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.27800562324273664</v>
+        <v>0.2810046860356139</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>7703.68</v>
+        <v>7671.68</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>3851.84</v>
+        <v>7671.68</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.6986533665835406</v>
+        <v>3.5483076923076924</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>232.5</v>
+        <v>465</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>233.5</v>
+        <v>467</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>232</v>
+        <v>464</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>236.5</v>
+        <v>473</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>242</v>
+        <v>484</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>1176.5</v>
+        <v>2353</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>308</v>
+        <v>616</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>283</v>
+        <v>566</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>287</v>
+        <v>574</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>306</v>
+        <v>612</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>1184</v>
+        <v>2368</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>1003</v>
+        <v>1046</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.18403669724770641</v>
+        <v>0.19192660550458715</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5184,23 +5184,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>3245.3199999999997</v>
+        <v>3277.32</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.20710402042118697</v>
+        <v>0.20914613911933633</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>12424.68</v>
+        <v>12392.68</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>6212.34</v>
+        <v>12392.68</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.2356131605184442</v>
+        <v>3.1331931166347995</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7CD8F8-BD23-462B-BBAE-C74421378BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C798EDCC-49C5-4256-8B58-ADF8FFA87759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3604,18 +3604,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.96296296296296291</v>
+        <v>1</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="94">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3710,34 +3710,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15+10+10+16+12</f>
-        <v>220</v>
+        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15+10+10+16+12+20</f>
+        <v>240</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.36666666666666664</v>
+        <v>0.4</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.54260869565217396</v>
+        <v>0.56173913043478263</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>263</v>
-      </c>
-      <c r="N4" s="10">
+        <v>252</v>
+      </c>
+      <c r="N4" s="10" t="e">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>263</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.4181818181818182</v>
+        <v>1.3458333333333334</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3767,38 +3767,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15+12+1+6+8+8</f>
-        <v>172</v>
+        <f>4+8+7+17+7+3+2+5+7+14+20+10+18+15+12+1+6+8+8+15</f>
+        <v>187</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.28666666666666668</v>
+        <v>0.31166666666666665</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.29636363636363638</v>
+        <v>0.31454545454545457</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>387</v>
-      </c>
-      <c r="N5" s="14">
+        <v>377</v>
+      </c>
+      <c r="N5" s="14" t="e">
         <f t="shared" si="3"/>
-        <v>387</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.94767441860465118</v>
+        <v>0.92513368983957223</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.0338266384778012</v>
+        <v>1.0092367525522608</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3846,9 +3846,9 @@
         <f t="shared" si="2"/>
         <v>503.68</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="14" t="e">
         <f t="shared" si="3"/>
-        <v>503.68</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3906,9 +3906,9 @@
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
         <v>483</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="14" t="e">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>483</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
@@ -3945,38 +3945,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13+12+16+12+14+18+15</f>
-        <v>234</v>
+        <f>10+10+0+14+6+10+11+11+8+7+9+24+14+13+12+16+12+14+18+15+18</f>
+        <v>252</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.60869565217391308</v>
+        <v>0.62434782608695649</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>225</v>
-      </c>
-      <c r="N8" s="14">
+        <v>216</v>
+      </c>
+      <c r="N8" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>225</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.4957264957264957</v>
+        <v>1.4246031746031746</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.5607580824972129</v>
+        <v>1.4865424430641823</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4019,9 +4019,9 @@
         <f t="shared" si="5"/>
         <v>550</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>550</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4067,27 +4067,27 @@
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <v>1460</v>
+        <v>1891</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.31601731601731603</v>
+        <v>0.40930735930735929</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>3160</v>
-      </c>
-      <c r="N10" s="14">
+        <v>2729</v>
+      </c>
+      <c r="N10" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>3160</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>14.897959183673469</v>
+        <v>19.295918367346939</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.64493329799452248</v>
+        <v>0.83532114144359038</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4135,9 +4135,9 @@
         <f t="shared" si="5"/>
         <v>650</v>
       </c>
-      <c r="N11" s="14">
+      <c r="N11" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>650</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4192,9 +4192,9 @@
         <f t="shared" si="5"/>
         <v>550</v>
       </c>
-      <c r="N12" s="14">
+      <c r="N12" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>550</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4239,9 +4239,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N13" s="14">
+      <c r="N13" s="14" t="e">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O13" s="72" t="e">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
@@ -4288,9 +4288,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="14" t="e">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O14" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4337,9 +4337,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="14" t="e">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O15" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4392,9 +4392,9 @@
         <f t="shared" si="5"/>
         <v>900</v>
       </c>
-      <c r="N16" s="14">
+      <c r="N16" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>900</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4435,9 +4435,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N17" s="14">
+      <c r="N17" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O17" s="72"/>
       <c r="P17" s="14"/>
@@ -4472,9 +4472,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N18" s="77">
+      <c r="N18" s="77" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O18" s="78"/>
       <c r="P18" s="39"/>
@@ -4501,11 +4501,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>845</v>
+        <v>898</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.16900000000000001</v>
+        <v>0.17960000000000001</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4513,23 +4513,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>2998.32</v>
+        <v>3459.32</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.2810046860356139</v>
+        <v>0.32420993439550144</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>7671.68</v>
-      </c>
-      <c r="N19" s="83">
+        <v>7210.68</v>
+      </c>
+      <c r="N19" s="83" t="e">
         <f t="shared" si="6"/>
-        <v>7671.68</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.5483076923076924</v>
+        <v>3.852249443207127</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4580,9 +4580,9 @@
         <f t="shared" si="5"/>
         <v>465</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="10" t="e">
         <f t="shared" si="6"/>
-        <v>465</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4636,9 +4636,9 @@
         <f t="shared" si="5"/>
         <v>467</v>
       </c>
-      <c r="N21" s="14">
+      <c r="N21" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>467</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4692,9 +4692,9 @@
         <f t="shared" si="5"/>
         <v>464</v>
       </c>
-      <c r="N22" s="14">
+      <c r="N22" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>464</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4748,9 +4748,9 @@
         <f t="shared" si="5"/>
         <v>473</v>
       </c>
-      <c r="N23" s="14">
+      <c r="N23" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>473</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4804,9 +4804,9 @@
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
-      <c r="N24" s="77">
+      <c r="N24" s="77" t="e">
         <f t="shared" si="6"/>
-        <v>484</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4860,9 +4860,9 @@
         <f t="shared" si="5"/>
         <v>2353</v>
       </c>
-      <c r="N25" s="83">
+      <c r="N25" s="83" t="e">
         <f t="shared" si="6"/>
-        <v>2353</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4917,9 +4917,9 @@
         <f t="shared" si="5"/>
         <v>616</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="10" t="e">
         <f t="shared" si="6"/>
-        <v>616</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4973,9 +4973,9 @@
         <f t="shared" si="5"/>
         <v>566</v>
       </c>
-      <c r="N27" s="14">
+      <c r="N27" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>566</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5029,9 +5029,9 @@
         <f t="shared" si="5"/>
         <v>574</v>
       </c>
-      <c r="N28" s="14">
+      <c r="N28" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>574</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5085,9 +5085,9 @@
         <f t="shared" si="5"/>
         <v>612</v>
       </c>
-      <c r="N29" s="77">
+      <c r="N29" s="77" t="e">
         <f t="shared" si="6"/>
-        <v>612</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5141,9 +5141,9 @@
         <f t="shared" si="5"/>
         <v>2368</v>
       </c>
-      <c r="N30" s="83">
+      <c r="N30" s="83" t="e">
         <f t="shared" si="6"/>
-        <v>2368</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>1046</v>
+        <v>1099</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.19192660550458715</v>
+        <v>0.20165137614678899</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5184,23 +5184,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>3277.32</v>
+        <v>3738.32</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.20914613911933633</v>
+        <v>0.23856541161455011</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>12392.68</v>
-      </c>
-      <c r="N31" s="92">
+        <v>11931.68</v>
+      </c>
+      <c r="N31" s="92" t="e">
         <f t="shared" si="6"/>
-        <v>12392.68</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.1331931166347995</v>
+        <v>3.4015650591446773</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>
